--- a/Templates/bulkImport/config/construct_DCR_config_sslr.xlsx
+++ b/Templates/bulkImport/config/construct_DCR_config_sslr.xlsx
@@ -13,84 +13,6 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>USER</author>
-  </authors>
-  <commentList>
-    <comment ref="F5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Times New Roman"/>
-            <charset val="0"/>
-          </rPr>
-          <t>Date Format:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Times New Roman"/>
-            <charset val="0"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Times New Roman"/>
-            <charset val="0"/>
-          </rPr>
-          <t>2024-01-01</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="V5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Times New Roman"/>
-            <charset val="0"/>
-          </rPr>
-          <t>Date Format:
-2024-01-01</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AA5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Times New Roman"/>
-            <charset val="0"/>
-          </rPr>
-          <t>Date Format:
-2024-01-01</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Times New Roman"/>
-            <charset val="0"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="63">
   <si>
@@ -293,7 +215,7 @@
     <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="179" formatCode="_-&quot;RM&quot;* #,##0_-;\-&quot;RM&quot;* #,##0_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -450,17 +372,6 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="Times New Roman"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Times New Roman"/>
-      <charset val="0"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1673,6 +1584,5 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Templates/bulkImport/config/construct_DCR_config_sslr.xlsx
+++ b/Templates/bulkImport/config/construct_DCR_config_sslr.xlsx
@@ -13,6 +13,84 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>USER</author>
+  </authors>
+  <commentList>
+    <comment ref="F5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t>Date Format:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t>2024-01-01</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t>Date Format:
+2024-01-01</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AA5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t>Date Format:
+2024-01-01</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="63">
   <si>
@@ -215,7 +293,7 @@
     <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="179" formatCode="_-&quot;RM&quot;* #,##0_-;\-&quot;RM&quot;* #,##0_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -372,6 +450,17 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1584,5 +1673,6 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>